--- a/raw_data/ice_on_dates_20250414.xlsx
+++ b/raw_data/ice_on_dates_20250414.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Gagers/Documents/Thesis and Lab/Ice Phenology Project/Ice_Pheno/Input_Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaga3666/repos/Ice_Pheno/raw_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A087BE-BB60-7042-99E0-029693E07B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84C4C4B-E120-F24E-A182-43BC71187C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15300" yWindow="4520" windowWidth="14100" windowHeight="13580" xr2:uid="{2030D7F7-1607-1B48-96B6-4E322D6653BA}"/>
   </bookViews>
@@ -426,6 +426,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6C9C687-AD29-4441-A732-C2BF8DB8A695}">
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
